--- a/data/02-fixed-motivation-wander/solution2_records.xlsx
+++ b/data/02-fixed-motivation-wander/solution2_records.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liyihan/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liyihan/dev/ai-town-island-research/data/02-fixed-motivation-wander/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C60823-7C74-6349-8355-AB3BD7180BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4898B1B2-714A-3440-A983-F279AC37CA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40" yWindow="1500" windowWidth="28040" windowHeight="16940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40" yWindow="660" windowWidth="28040" windowHeight="16880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="message" sheetId="1" r:id="rId1"/>
@@ -7287,7 +7287,7 @@
         <v>121</v>
       </c>
       <c r="D194" s="3" t="str">
-        <f t="shared" ref="D194:D257" si="3">MID(C194,FIND(":",C194)+1,99)</f>
+        <f t="shared" ref="D194:D251" si="3">MID(C194,FIND(":",C194)+1,99)</f>
         <v>1140</v>
       </c>
       <c r="E194" s="3" t="s">
@@ -8508,7 +8508,7 @@
   <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.1640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="8.33203125" style="3" customWidth="1"/>
     <col min="4" max="4" width="11" style="3" customWidth="1"/>
@@ -8561,7 +8561,7 @@
         <v>66</v>
       </c>
       <c r="F2" s="3" t="str">
-        <f>MID(E2,FIND(":",E2)+1,99)</f>
+        <f t="shared" ref="F2:F37" si="0">MID(E2,FIND(":",E2)+1,99)</f>
         <v>26</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -8588,7 +8588,7 @@
         <v>66</v>
       </c>
       <c r="F3" s="3" t="str">
-        <f>MID(E3,FIND(":",E3)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -8615,7 +8615,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="str">
-        <f>MID(E4,FIND(":",E4)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -8642,7 +8642,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="str">
-        <f>MID(E5,FIND(":",E5)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -8669,7 +8669,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="3" t="str">
-        <f>MID(E6,FIND(":",E6)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -8696,7 +8696,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="3" t="str">
-        <f>MID(E7,FIND(":",E7)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -8723,7 +8723,7 @@
         <v>77</v>
       </c>
       <c r="F8" s="3" t="str">
-        <f>MID(E8,FIND(":",E8)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>99</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -8750,7 +8750,7 @@
         <v>77</v>
       </c>
       <c r="F9" s="3" t="str">
-        <f>MID(E9,FIND(":",E9)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>99</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -8777,7 +8777,7 @@
         <v>54</v>
       </c>
       <c r="F10" s="3" t="str">
-        <f>MID(E10,FIND(":",E10)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>204</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -8804,7 +8804,7 @@
         <v>139</v>
       </c>
       <c r="F11" s="3" t="str">
-        <f>MID(E11,FIND(":",E11)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>212</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -8831,7 +8831,7 @@
         <v>161</v>
       </c>
       <c r="F12" s="3" t="str">
-        <f>MID(E12,FIND(":",E12)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>218</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -8858,7 +8858,7 @@
         <v>161</v>
       </c>
       <c r="F13" s="3" t="str">
-        <f>MID(E13,FIND(":",E13)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>218</v>
       </c>
       <c r="G13" s="3" t="s">
@@ -8885,7 +8885,7 @@
         <v>17</v>
       </c>
       <c r="F14" s="3" t="str">
-        <f>MID(E14,FIND(":",E14)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>370</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -8912,7 +8912,7 @@
         <v>17</v>
       </c>
       <c r="F15" s="3" t="str">
-        <f>MID(E15,FIND(":",E15)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>370</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -8939,7 +8939,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="3" t="str">
-        <f>MID(E16,FIND(":",E16)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>386</v>
       </c>
       <c r="G16" s="3" t="s">
@@ -8966,7 +8966,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="3" t="str">
-        <f>MID(E17,FIND(":",E17)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>386</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -8993,7 +8993,7 @@
         <v>35</v>
       </c>
       <c r="F18" s="3" t="str">
-        <f>MID(E18,FIND(":",E18)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>400</v>
       </c>
       <c r="G18" s="3" t="s">
@@ -9020,7 +9020,7 @@
         <v>35</v>
       </c>
       <c r="F19" s="3" t="str">
-        <f>MID(E19,FIND(":",E19)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>400</v>
       </c>
       <c r="G19" s="3" t="s">
@@ -9047,7 +9047,7 @@
         <v>253</v>
       </c>
       <c r="F20" s="3" t="str">
-        <f>MID(E20,FIND(":",E20)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>496</v>
       </c>
       <c r="G20" s="3" t="s">
@@ -9074,7 +9074,7 @@
         <v>113</v>
       </c>
       <c r="F21" s="3" t="str">
-        <f>MID(E21,FIND(":",E21)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>516</v>
       </c>
       <c r="G21" s="3" t="s">
@@ -9101,7 +9101,7 @@
         <v>84</v>
       </c>
       <c r="F22" s="3" t="str">
-        <f>MID(E22,FIND(":",E22)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>605</v>
       </c>
       <c r="G22" s="3" t="s">
@@ -9128,7 +9128,7 @@
         <v>84</v>
       </c>
       <c r="F23" s="3" t="str">
-        <f>MID(E23,FIND(":",E23)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>605</v>
       </c>
       <c r="G23" s="3" t="s">
@@ -9155,7 +9155,7 @@
         <v>62</v>
       </c>
       <c r="F24" s="3" t="str">
-        <f>MID(E24,FIND(":",E24)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>638</v>
       </c>
       <c r="G24" s="3" t="s">
@@ -9182,7 +9182,7 @@
         <v>117</v>
       </c>
       <c r="F25" s="3" t="str">
-        <f>MID(E25,FIND(":",E25)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>704</v>
       </c>
       <c r="G25" s="3" t="s">
@@ -9209,7 +9209,7 @@
         <v>58</v>
       </c>
       <c r="F26" s="3" t="str">
-        <f>MID(E26,FIND(":",E26)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>871</v>
       </c>
       <c r="G26" s="3" t="s">
@@ -9236,7 +9236,7 @@
         <v>58</v>
       </c>
       <c r="F27" s="3" t="str">
-        <f>MID(E27,FIND(":",E27)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>871</v>
       </c>
       <c r="G27" s="3" t="s">
@@ -9263,7 +9263,7 @@
         <v>174</v>
       </c>
       <c r="F28" s="3" t="str">
-        <f>MID(E28,FIND(":",E28)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>897</v>
       </c>
       <c r="G28" s="3" t="s">
@@ -9290,7 +9290,7 @@
         <v>174</v>
       </c>
       <c r="F29" s="3" t="str">
-        <f>MID(E29,FIND(":",E29)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>897</v>
       </c>
       <c r="G29" s="3" t="s">
@@ -9317,7 +9317,7 @@
         <v>27</v>
       </c>
       <c r="F30" s="3" t="str">
-        <f>MID(E30,FIND(":",E30)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>1052</v>
       </c>
       <c r="G30" s="3" t="s">
@@ -9344,7 +9344,7 @@
         <v>27</v>
       </c>
       <c r="F31" s="3" t="str">
-        <f>MID(E31,FIND(":",E31)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>1052</v>
       </c>
       <c r="G31" s="3" t="s">
@@ -9371,7 +9371,7 @@
         <v>121</v>
       </c>
       <c r="F32" s="3" t="str">
-        <f>MID(E32,FIND(":",E32)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>1140</v>
       </c>
       <c r="G32" s="3" t="s">
@@ -9398,7 +9398,7 @@
         <v>31</v>
       </c>
       <c r="F33" s="3" t="str">
-        <f>MID(E33,FIND(":",E33)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>1153</v>
       </c>
       <c r="G33" s="3" t="s">
@@ -9425,7 +9425,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="3" t="str">
-        <f>MID(E34,FIND(":",E34)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>1281</v>
       </c>
       <c r="G34" s="3" t="s">
@@ -9452,7 +9452,7 @@
         <v>44</v>
       </c>
       <c r="F35" s="3" t="str">
-        <f>MID(E35,FIND(":",E35)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>1308</v>
       </c>
       <c r="G35" s="3" t="s">
@@ -9479,7 +9479,7 @@
         <v>44</v>
       </c>
       <c r="F36" s="3" t="str">
-        <f>MID(E36,FIND(":",E36)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>1308</v>
       </c>
       <c r="G36" s="3" t="s">
@@ -9506,7 +9506,7 @@
         <v>7</v>
       </c>
       <c r="F37" s="3" t="str">
-        <f>MID(E37,FIND(":",E37)+1,99)</f>
+        <f t="shared" si="0"/>
         <v>1323</v>
       </c>
       <c r="G37" s="3" t="s">
